--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1916,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79911987</v>
+        <v>95592754</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,56 +1928,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
+          <t>Älgered, Nordanstig, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601168.1718535598</v>
+        <v>601187.4343710395</v>
       </c>
       <c r="R12" t="n">
-        <v>6877648.30086042</v>
+        <v>6877680.822077918</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2001,22 +1996,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2021-08-20</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2043,10 +2038,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95592754</v>
+        <v>111979337</v>
       </c>
       <c r="B13" t="n">
-        <v>90697</v>
+        <v>89111</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,51 +2050,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>256703</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älgered, Nordanstig, Hls</t>
+          <t>Älgered, Nordanstig (Älgered, Nordanstig), Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>601187.4343710395</v>
+        <v>601184</v>
       </c>
       <c r="R13" t="n">
-        <v>6877680.822077918</v>
+        <v>6877674</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2123,22 +2109,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Vid stigförgrening invid äldre tall. Se bilder.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2165,10 +2156,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111979337</v>
+        <v>112481246</v>
       </c>
       <c r="B14" t="n">
-        <v>89111</v>
+        <v>90399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2177,42 +2168,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Älgered, Nordanstig (Älgered, Nordanstig), Hls</t>
+          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun (Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun), Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>601184</v>
+        <v>601210</v>
       </c>
       <c r="R14" t="n">
-        <v>6877674</v>
+        <v>6877659</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2236,27 +2227,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Vid stigförgrening invid äldre tall. Se bilder.</t>
+          <t>I kanten av stigen ned mot båtplats. Västra kanten I böjen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2283,10 +2274,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112481246</v>
+        <v>112481511</v>
       </c>
       <c r="B15" t="n">
-        <v>90399</v>
+        <v>90921</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2299,35 +2290,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1958</v>
+        <v>1435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun (Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun), Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>601210</v>
+        <v>601183</v>
       </c>
       <c r="R15" t="n">
-        <v>6877659</v>
+        <v>6877672</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2354,27 +2355,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>I kanten av stigen ned mot båtplats. Västra kanten I böjen.</t>
+          <t>I slänten ner mot en större svacka i terrängen. Ca 3 m från stigen. Tydlig doft av bittermandel.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2383,6 +2384,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2398,135 +2400,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>112481511</v>
-      </c>
-      <c r="B16" t="n">
-        <v>90921</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1435</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bitter taggsvamp</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Hydnellum fennicum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun (Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun), Hls</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>601183</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6877672</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Nordanstig</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Bergsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>I slänten ner mot en större svacka i terrängen. Ca 3 m från stigen. Tydlig doft av bittermandel.</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79911383</v>
+        <v>112481511</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>1435</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -719,19 +714,20 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
+          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601221.9920501495</v>
+        <v>601183</v>
       </c>
       <c r="R2" t="n">
-        <v>6877626.414523352</v>
+        <v>6877671</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I slänten ner mot en större svacka i terrängen. Ca 3 m från stigen. Tydlig doft av bittermandel.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,6 +780,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79911471</v>
+        <v>112481246</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,52 +810,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
+          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601214.1428900524</v>
+        <v>601210</v>
       </c>
       <c r="R3" t="n">
-        <v>6877652.959889085</v>
+        <v>6877659</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,22 +865,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-14</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I kanten av stigen ned mot båtplats. Västra kanten I böjen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,68 +912,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79912108</v>
+        <v>79911509</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>601195.2665941047</v>
+        <v>601202</v>
       </c>
       <c r="R4" t="n">
-        <v>6877623.268659084</v>
+        <v>6877684</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1014,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,15 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79911785</v>
+        <v>79911729</v>
       </c>
       <c r="B5" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1059,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1097,17 +1070,17 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
+          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>601162.7265845037</v>
+        <v>601182</v>
       </c>
       <c r="R5" t="n">
-        <v>6877641.561205165</v>
+        <v>6877686</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1146,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,68 +1146,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79911674</v>
+        <v>79911785</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
+          <t>Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>601191.6148361181</v>
+        <v>601163</v>
       </c>
       <c r="R6" t="n">
-        <v>6877666.852419161</v>
+        <v>6877642</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1263,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,60 +1263,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79911509</v>
+        <v>79911471</v>
       </c>
       <c r="B7" t="n">
-        <v>90639</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3100</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>601202.3932067641</v>
+        <v>601214</v>
       </c>
       <c r="R7" t="n">
-        <v>6877684.08685285</v>
+        <v>6877653</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1385,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1395,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1422,15 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79911815</v>
+        <v>79911674</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,15 +1415,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1473,13 +1435,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>601168.8742234779</v>
+        <v>601192</v>
       </c>
       <c r="R8" t="n">
-        <v>6877656.308594085</v>
+        <v>6877667</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1508,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1518,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1545,60 +1507,56 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79912133</v>
+        <v>79911815</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>601230.1014623779</v>
+        <v>601169</v>
       </c>
       <c r="R9" t="n">
-        <v>6877606.924009011</v>
+        <v>6877656</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1630,7 +1588,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1640,7 +1598,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,63 +1625,63 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79911729</v>
+        <v>79911850</v>
       </c>
       <c r="B10" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>601182.0955178874</v>
+        <v>601169</v>
       </c>
       <c r="R10" t="n">
-        <v>6877686.300633481</v>
+        <v>6877647</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1752,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1762,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,15 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79911850</v>
+        <v>79911987</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1824,7 +1777,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1844,13 +1797,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>601168.6699235105</v>
+        <v>601168</v>
       </c>
       <c r="R11" t="n">
-        <v>6877647.376079012</v>
+        <v>6877648</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1916,37 +1869,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95592754</v>
+        <v>79912108</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1956,23 +1904,28 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Älgered, Nordanstig, Hls</t>
+          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>601187.4343710395</v>
+        <v>601195</v>
       </c>
       <c r="R12" t="n">
-        <v>6877680.822077918</v>
+        <v>6877623</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1996,22 +1949,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-08-20</t>
+          <t>2019-09-14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2041,16 +1994,11 @@
         <v>111979337</v>
       </c>
       <c r="B13" t="n">
-        <v>89111</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2075,7 +2023,7 @@
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Älgered, Nordanstig (Älgered, Nordanstig), Hls</t>
+          <t>Älgered, Nordanstig, Älgered, Nordanstig, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2153,253 +2101,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>112481246</v>
-      </c>
-      <c r="B14" t="n">
-        <v>90399</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1958</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Lammticka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Albatrellus subrubescens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Murrill) Pouzar</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun (Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun), Hls</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>601210</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6877659</v>
-      </c>
-      <c r="S14" t="n">
-        <v>25</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Nordanstig</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Bergsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>I kanten av stigen ned mot båtplats. Västra kanten I böjen.</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>112481511</v>
-      </c>
-      <c r="B15" t="n">
-        <v>90921</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>1435</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bitter taggsvamp</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Hydnellum fennicum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun (Barrtjärnen, Bergsjövägen, Ede, Nordanstigs kommun), Hls</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>601183</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6877672</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Nordanstig</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Bergsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2023-09-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>I slänten ner mot en större svacka i terrängen. Ca 3 m från stigen. Tydlig doft av bittermandel.</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31224-2022 artfynd.xlsx
+++ b/artfynd/A 31224-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112481511</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112481246</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911509</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911729</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1260,6 +1285,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911785</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911471</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1504,6 +1539,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911674</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1622,6 +1662,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911815</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1744,6 +1789,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911850</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1866,6 +1916,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79911987</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1988,6 +2043,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79912108</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2101,8 +2161,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111979337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>